--- a/excel/file/example.xlsx
+++ b/excel/file/example.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\office\excel\file\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A7B86D-8F12-4CEA-91ED-732060B2D0F7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="30" windowWidth="25875" windowHeight="12345"/>
+    <workbookView xWindow="3030" yWindow="1650" windowWidth="21120" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$71:$I$81</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
@@ -743,7 +749,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -996,9 +1002,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1041,10 +1044,13 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="强调文字颜色 1" xfId="1" builtinId="29"/>
+    <cellStyle name="着色 1" xfId="1" builtinId="29"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
@@ -1175,12 +1181,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
@@ -1194,7 +1203,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1220,6 +1228,13 @@
           </c:tx>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
@@ -1228,41 +1243,31 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>'[1]第二学期成绩表 (2)'!$A$209:$B$213</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="5"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>安倍晋三</c:v>
+                    <c:v>英语</c:v>
                   </c:pt>
                   <c:pt idx="1">
                     <c:v>英语</c:v>
                   </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>张4</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
+                  <c:pt idx="2">
                     <c:v>数学</c:v>
                   </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>张3</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
+                  <c:pt idx="3">
                     <c:v>数学</c:v>
                   </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>张2</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
+                  <c:pt idx="4">
                     <c:v>英语</c:v>
                   </c:pt>
                 </c:lvl>
@@ -1271,7 +1276,16 @@
                     <c:v>张1</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>英语</c:v>
+                    <c:v>张2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>张3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>张4</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>安倍晋三</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -1301,6 +1315,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BA8E-4950-96DA-EFFB1922D068}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1322,9 +1341,9 @@
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1346,7 +1365,6 @@
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:txPr>
             <a:bodyPr rot="0" vert="wordArtVertRtl"/>
@@ -1370,7 +1388,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1386,7 +1403,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
@@ -1415,7 +1432,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1497,6 +1513,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9D1C-4FB2-B5C7-D13BE6EF8D9A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1579,6 +1600,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9D1C-4FB2-B5C7-D13BE6EF8D9A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1600,6 +1626,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1648,6 +1675,7 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1661,7 +1689,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1693,7 +1720,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -1725,7 +1758,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="图表 2"/>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -1893,7 +1932,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Users" refreshedDate="43760.460026620371" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="10">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Users" refreshedDate="43760.460026620371" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="10" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A113:J123" sheet="第二学期成绩表 (2)" r:id="rId2"/>
   </cacheSource>
@@ -2115,7 +2154,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="数据透视表2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A125:D130" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
@@ -2194,12 +2233,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="数据透视表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A132:C137" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -2269,20 +2311,23 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表2_4" displayName="表2_4" ref="A34:D39" totalsRowShown="0">
-  <autoFilter ref="A34:D39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2_4" displayName="表2_4" ref="A34:D39" totalsRowShown="0">
+  <autoFilter ref="A34:D39" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="第一列"/>
-    <tableColumn id="2" name="第二列"/>
-    <tableColumn id="3" name="求和" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="第一列"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="第二列"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="求和" dataDxfId="0">
       <calculatedColumnFormula>表2_4[[#This Row],[第一列]]+表2_4[[#This Row],[第二列]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" name="季节"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="季节"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2331,7 +2376,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2364,9 +2409,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2399,6 +2461,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2574,7 +2653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J259"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
@@ -2699,12 +2778,12 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
@@ -3429,240 +3508,240 @@
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A86" s="19" t="s">
+      <c r="A86" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B86" s="20" t="s">
+      <c r="B86" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="C86" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="D86" s="20" t="s">
+      <c r="D86" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E86" s="20" t="s">
+      <c r="E86" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F86" s="21" t="s">
+      <c r="F86" s="20" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A87" s="22" t="s">
+      <c r="A87" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B87" s="23" t="s">
+      <c r="B87" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="C87" s="23">
+      <c r="C87" s="22">
         <v>23</v>
       </c>
-      <c r="D87" s="23" t="s">
+      <c r="D87" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="E87" s="23" t="s">
+      <c r="E87" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="F87" s="24">
+      <c r="F87" s="23">
         <v>4200</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A88" s="25" t="s">
+      <c r="A88" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B88" s="26" t="s">
+      <c r="B88" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C88" s="26">
+      <c r="C88" s="25">
         <v>25</v>
       </c>
-      <c r="D88" s="26" t="s">
+      <c r="D88" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E88" s="26" t="s">
+      <c r="E88" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="F88" s="27">
+      <c r="F88" s="26">
         <v>4400</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A89" s="22" t="s">
+      <c r="A89" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B89" s="23" t="s">
+      <c r="B89" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C89" s="23">
+      <c r="C89" s="22">
         <v>27</v>
       </c>
-      <c r="D89" s="23" t="s">
+      <c r="D89" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="E89" s="23" t="s">
+      <c r="E89" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F89" s="24">
+      <c r="F89" s="23">
         <v>4300</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A90" s="25" t="s">
+      <c r="A90" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B90" s="26" t="s">
+      <c r="B90" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C90" s="26">
+      <c r="C90" s="25">
         <v>41</v>
       </c>
-      <c r="D90" s="26" t="s">
+      <c r="D90" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E90" s="26" t="s">
+      <c r="E90" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="F90" s="27">
+      <c r="F90" s="26">
         <v>4800</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A91" s="22"/>
-      <c r="B91" s="23"/>
-      <c r="C91" s="23"/>
-      <c r="D91" s="28" t="s">
+      <c r="A91" s="21"/>
+      <c r="B91" s="22"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="E91" s="23"/>
-      <c r="F91" s="24">
+      <c r="E91" s="22"/>
+      <c r="F91" s="23">
         <f>SUBTOTAL(1,F87:F90)</f>
         <v>4425</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A92" s="25" t="s">
+      <c r="A92" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B92" s="26" t="s">
+      <c r="B92" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C92" s="26">
+      <c r="C92" s="25">
         <v>23</v>
       </c>
-      <c r="D92" s="26" t="s">
+      <c r="D92" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="E92" s="26" t="s">
+      <c r="E92" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F92" s="27">
+      <c r="F92" s="26">
         <v>4100</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A93" s="22" t="s">
+      <c r="A93" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B93" s="23" t="s">
+      <c r="B93" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="C93" s="23">
+      <c r="C93" s="22">
         <v>26</v>
       </c>
-      <c r="D93" s="23" t="s">
+      <c r="D93" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E93" s="23" t="s">
+      <c r="E93" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F93" s="24">
+      <c r="F93" s="23">
         <v>4500</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A94" s="25" t="s">
+      <c r="A94" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B94" s="26" t="s">
+      <c r="B94" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C94" s="26">
+      <c r="C94" s="25">
         <v>26</v>
       </c>
-      <c r="D94" s="26" t="s">
+      <c r="D94" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="E94" s="26" t="s">
+      <c r="E94" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F94" s="27">
+      <c r="F94" s="26">
         <v>4500</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A95" s="22" t="s">
+      <c r="A95" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B95" s="23" t="s">
+      <c r="B95" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C95" s="23">
+      <c r="C95" s="22">
         <v>21</v>
       </c>
-      <c r="D95" s="23" t="s">
+      <c r="D95" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E95" s="23" t="s">
+      <c r="E95" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F95" s="24">
+      <c r="F95" s="23">
         <v>4700</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A96" s="25" t="s">
+      <c r="A96" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="26" t="s">
+      <c r="B96" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C96" s="26">
+      <c r="C96" s="25">
         <v>22</v>
       </c>
-      <c r="D96" s="26" t="s">
+      <c r="D96" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="E96" s="26" t="s">
+      <c r="E96" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="F96" s="27">
+      <c r="F96" s="26">
         <v>4100</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A97" s="22"/>
-      <c r="B97" s="23"/>
-      <c r="C97" s="23"/>
-      <c r="D97" s="28" t="s">
+      <c r="A97" s="21"/>
+      <c r="B97" s="22"/>
+      <c r="C97" s="22"/>
+      <c r="D97" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="E97" s="23"/>
-      <c r="F97" s="24">
+      <c r="E97" s="22"/>
+      <c r="F97" s="23">
         <f>SUBTOTAL(1,F92:F96)</f>
         <v>4380</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A98" s="15"/>
-      <c r="B98" s="16"/>
-      <c r="C98" s="16"/>
-      <c r="D98" s="18" t="s">
+      <c r="A98" s="14"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E98" s="16"/>
-      <c r="F98" s="17">
+      <c r="E98" s="15"/>
+      <c r="F98" s="16">
         <f>SUBTOTAL(1,F87:F96)</f>
         <v>4400</v>
       </c>
@@ -4762,7 +4841,7 @@
       </c>
       <c r="B182" s="10">
         <f ca="1">TODAY()</f>
-        <v>44039</v>
+        <v>44295</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.15">
@@ -4771,7 +4850,7 @@
       </c>
       <c r="B183">
         <f ca="1">YEAR(TODAY())</f>
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.15">
@@ -4780,7 +4859,7 @@
       </c>
       <c r="B184">
         <f ca="1">MONTH(TODAY())</f>
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.15">
@@ -4835,7 +4914,7 @@
       </c>
       <c r="B190" s="12">
         <f ca="1">NOW()</f>
-        <v>44039.334288194441</v>
+        <v>44295.662256828706</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.15">
@@ -4844,7 +4923,7 @@
       </c>
       <c r="B191">
         <f ca="1">WEEKDAY(B190,2)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.15">
@@ -5169,7 +5248,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A71:I81"/>
+  <autoFilter ref="A71:I81" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="1">
     <mergeCell ref="A18:D18"/>
@@ -5223,10 +5302,10 @@
     <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C103:C109">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C103:C109" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"本科,大专"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B103:B109">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B103:B109" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"男,女"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5239,7 +5318,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup manualMax="0" manualMin="0" displayEmptyCellsAs="gap">
+        <x14:sparklineGroup manualMax="0" manualMin="0" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000000000000}">
           <x14:colorSeries theme="4" tint="-0.499984740745262"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -5270,7 +5349,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
@@ -5280,7 +5359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>

--- a/excel/file/example.xlsx
+++ b/excel/file/example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24002"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\office\excel\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A7B86D-8F12-4CEA-91ED-732060B2D0F7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B88EE0-3844-4BE7-A3F7-C584AF979E60}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="1650" windowWidth="21120" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3030" yWindow="1650" windowWidth="13980" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="B182" s="10">
         <f ca="1">TODAY()</f>
-        <v>44295</v>
+        <v>44297</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.15">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B190" s="12">
         <f ca="1">NOW()</f>
-        <v>44295.662256828706</v>
+        <v>44297.261731597224</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.15">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B191">
         <f ca="1">WEEKDAY(B190,2)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.15">

--- a/excel/file/example.xlsx
+++ b/excel/file/example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\office\excel\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B88EE0-3844-4BE7-A3F7-C584AF979E60}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16695E91-6285-4F3D-98A3-C55F52687576}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="1650" windowWidth="13980" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45" yWindow="825" windowWidth="13185" windowHeight="13935" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -2029,7 +2029,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="10">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
   <r>
     <n v="120104"/>
     <s v="成龙"/>
@@ -2154,7 +2154,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="数据透视表2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="数据透视表2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A125:D130" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
@@ -2241,7 +2241,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="数据透视表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="数据透视表1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A132:C137" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -2320,7 +2320,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2_4" displayName="表2_4" ref="A34:D39" totalsRowShown="0">
-  <autoFilter ref="A34:D39" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A34:D39" xr:uid="{F0E02479-4999-47A6-8969-788D462DC505}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="第一列"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="第二列"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="B182" s="10">
         <f ca="1">TODAY()</f>
-        <v>44297</v>
+        <v>44299</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.15">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B190" s="12">
         <f ca="1">NOW()</f>
-        <v>44297.261731597224</v>
+        <v>44299.483517476852</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.15">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B191">
         <f ca="1">WEEKDAY(B190,2)</f>
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.15">
